--- a/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="340">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.282</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">The Yerles, people of the rising New Kingdom in Sierre Terre, trace their lineage back to slaves who escaped from Eulderna. Harboring deep-seated hatred towards the empire and everything it represents; they have established the pinnacle of mechanical civilizations in Sierre. Gifted with a heightened learning capacity, adept in handling mechanized armaments, they acquire feats faster than any other races.</t>
   </si>
   <si>
-    <t xml:space="preserve">シエラ・テールで急速に台頭してきた新王国イエルの民がイェルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
+    <t xml:space="preserve">シエラ・テールで急速に台頭してきた新王国イエルの民がイエルスです。彼らの祖先はエウダーナから脱走した奴隷であり、帝国と帝国の生み出した全てのものを憎んでいます。シエラ随一の機械文明を築き上げた彼らは、高い学習能力を持ち、機械武装の扱いにたけ、他の種族よりも早くフィートを獲得できます。</t>
   </si>
   <si>
     <t xml:space="preserve">eulderna</t>
@@ -338,6 +338,12 @@
     <t xml:space="preserve">スライム</t>
   </si>
   <si>
+    <t xml:space="preserve">Slimes are amorphous, gelatinous beings with bodies that lack a fixed shape. They may appear fragile and are often called the weakest of monsters, yet they possess a mysterious potential to absorb whatever they take in and transform it into their own strength. Even if you were to awaken one day as a slime, there would be no need to despair. That humble body is merely the beginning of an endless path of evolution.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スライムは不定形の体を持つ粘体生物です。見た目は頼りなく、最弱の魔物と呼ばれることもありますが、あらゆるものを取り込み、自らの力へと変えていく不思議な可能性を秘めています。もし目覚めたときに自分がスライムだったとしても、嘆く必要はありません。その体は、無限の進化へと続く始まりなのです。</t>
+  </si>
+  <si>
     <t xml:space="preserve">wolf</t>
   </si>
   <si>
@@ -716,7 +722,7 @@
     <t xml:space="preserve">神</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.19</t>
+    <t xml:space="preserve">EA 23.272</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 15.1</t>
@@ -743,6 +749,9 @@
     <t xml:space="preserve">Alpha 17.1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.278</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.27 fix 2</t>
   </si>
   <si>
@@ -1023,6 +1032,9 @@
   </si>
   <si>
     <t xml:space="preserve">古代螃蟹是最古老的螃蟹种族，靠近水源生活，根据栖息的地区进化为各种属性。基本上很好吃，而且根据属性的不同味道也会变化。它们的力量和体质都很强大，能用巨大的钳子拘束敌人，还可以吐出泡沫吐息。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">史莱姆是一种拥有不定形躯体的黏液生物。模样看起来无害，常被称为最弱小的魔物，却蕴含着吞噬万物并将其转化为自身力量的神奇潜能。即便苏醒时发现自己是个史莱姆，也无需哀叹。这副躯体正是通往无限进化的起点。</t>
   </si>
 </sst>
 </file>
@@ -1128,10 +1140,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1140,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1154,10 +1166,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1166,7 +1178,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1180,7 +1192,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1192,7 +1204,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1206,10 +1218,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1218,7 +1230,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1232,10 +1244,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1244,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1258,10 +1270,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -1270,7 +1282,7 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -1284,10 +1296,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -1296,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -1310,10 +1322,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1322,7 +1334,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1336,10 +1348,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1348,7 +1360,7 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -1362,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -1374,7 +1386,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1388,10 +1400,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1400,7 +1412,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1414,10 +1426,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1426,7 +1438,7 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="G14" t="s">
         <v>57</v>
@@ -1440,10 +1452,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -1452,7 +1464,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -1466,10 +1478,10 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -1478,7 +1490,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G16" t="s">
         <v>65</v>
@@ -1492,7 +1504,7 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
         <v>68</v>
@@ -1504,7 +1516,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G17" t="s">
         <v>69</v>
@@ -1518,7 +1530,7 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
         <v>72</v>
@@ -1530,7 +1542,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
@@ -1544,10 +1556,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1556,7 +1568,7 @@
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
@@ -1570,10 +1582,10 @@
         <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -1582,7 +1594,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G20" t="s">
         <v>81</v>
@@ -1596,10 +1608,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C21" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1608,7 +1620,7 @@
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="G21" t="s">
         <v>86</v>
@@ -1622,10 +1634,10 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
@@ -1641,10 +1653,10 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
         <v>91</v>
@@ -1660,10 +1672,10 @@
         <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -1679,10 +1691,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C25" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D25" t="s">
         <v>95</v>
@@ -1698,10 +1710,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -1717,10 +1729,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -1736,10 +1748,10 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1755,10 +1767,10 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D29" t="s">
         <v>103</v>
@@ -1774,10 +1786,10 @@
         <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -1785,1183 +1797,1190 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="F30" t="s">
+        <v>339</v>
+      </c>
+      <c r="G30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C33" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C37" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D37" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E38" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D39" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B43" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B44" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E44" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E45" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B46" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C46" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E49" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B51" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B52" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C52" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E52" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D53" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D54" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B56" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C56" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C57" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B58" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C58" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E58" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D59" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E59" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E60" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C61" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E61" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B62" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E62" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B63" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B65" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C65" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D65" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E65" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B66" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C66" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D66" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E66" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B68" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D68" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E68" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B69" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C69" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D69" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E69" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C70" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E70" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C71" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D71" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C72" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D72" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C73" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D73" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E73" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C74" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D74" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E74" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D75" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E75" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B76" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C76" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E76" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B77" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C77" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D77" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E77" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B78" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C78" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D78" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E78" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B79" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D79" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E79" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B80" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C80" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D80" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E80" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B81" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D81" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E81" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B82" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C82" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D82" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E82" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B83" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C83" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D83" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E83" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B84" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C84" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D84" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D85" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E85" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D86" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E86" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D87" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E87" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D88" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E88" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B89" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E89" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C90" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D90" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E90" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D91" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E91" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G91"/>
       <c r="H91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C92" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D92" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E92" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G92"/>
       <c r="H92"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="352">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>
@@ -281,6 +281,18 @@
     <t xml:space="preserve">古代蟹は最も古い蟹の種族で、水辺を好み、生息する地域に適応し様々な属性へと進化しています。基本的には美味しいものの、属性によって風味も変化します。筋力と耐久に秀で、その巨大なハサミで敵を拘束し、また泡のブレスを吐くことができます。</t>
   </si>
   <si>
+    <t xml:space="preserve">ratkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラトキン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">werewolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人狼</t>
+  </si>
+  <si>
     <t xml:space="preserve">goblin</t>
   </si>
   <si>
@@ -362,6 +374,15 @@
     <t xml:space="preserve">ウサギ</t>
   </si>
   <si>
+    <t xml:space="preserve">rabbitkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ravian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラビアン</t>
+  </si>
+  <si>
     <t xml:space="preserve">sheep</t>
   </si>
   <si>
@@ -749,6 +770,12 @@
     <t xml:space="preserve">Alpha 17.1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.293</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.278</t>
   </si>
   <si>
@@ -812,6 +839,12 @@
     <t xml:space="preserve">古代螃蟹</t>
   </si>
   <si>
+    <t xml:space="preserve">鼠人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狼人</t>
+  </si>
+  <si>
     <t xml:space="preserve">哥布林</t>
   </si>
   <si>
@@ -843,6 +876,9 @@
   </si>
   <si>
     <t xml:space="preserve">兔子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">兔人</t>
   </si>
   <si>
     <t xml:space="preserve">蜈蚣</t>
@@ -1140,10 +1176,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1152,7 +1188,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1166,10 +1202,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1178,7 +1214,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1192,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1204,7 +1240,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1218,10 +1254,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C6" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1230,7 +1266,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1244,10 +1280,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1256,7 +1292,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1270,10 +1306,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -1282,7 +1318,7 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -1296,10 +1332,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -1308,7 +1344,7 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -1322,10 +1358,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1334,7 +1370,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1348,10 +1384,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C11" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1360,7 +1396,7 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -1374,7 +1410,7 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -1386,7 +1422,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1400,10 +1436,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1412,7 +1448,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1426,10 +1462,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1438,7 +1474,7 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="G14" t="s">
         <v>57</v>
@@ -1452,10 +1488,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C15" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -1464,7 +1500,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -1478,10 +1514,10 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -1490,7 +1526,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="G16" t="s">
         <v>65</v>
@@ -1504,7 +1540,7 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
         <v>68</v>
@@ -1516,7 +1552,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="G17" t="s">
         <v>69</v>
@@ -1530,7 +1566,7 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
         <v>72</v>
@@ -1542,7 +1578,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
@@ -1556,10 +1592,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1568,7 +1604,7 @@
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
@@ -1582,10 +1618,10 @@
         <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -1594,7 +1630,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="G20" t="s">
         <v>81</v>
@@ -1608,10 +1644,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C21" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1620,7 +1656,7 @@
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="G21" t="s">
         <v>86</v>
@@ -1634,10 +1670,10 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
@@ -1653,48 +1689,48 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="C23" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
         <v>91</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" t="s">
+        <v>276</v>
+      </c>
+      <c r="D24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E24" t="s">
         <v>93</v>
-      </c>
-      <c r="B24" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" t="s">
-        <v>267</v>
-      </c>
-      <c r="D24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" t="s">
-        <v>94</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C25" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="D25" t="s">
         <v>95</v>
@@ -1710,10 +1746,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C26" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -1729,10 +1765,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -1748,10 +1784,10 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C28" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1767,10 +1803,10 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D29" t="s">
         <v>103</v>
@@ -1789,7 +1825,7 @@
         <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -1797,63 +1833,63 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="F30" t="s">
-        <v>339</v>
-      </c>
-      <c r="G30" t="s">
-        <v>107</v>
-      </c>
-      <c r="H30" t="s">
-        <v>108</v>
-      </c>
+      <c r="G30"/>
+      <c r="H30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" t="s">
+        <v>284</v>
+      </c>
+      <c r="D32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" t="s">
+        <v>351</v>
+      </c>
+      <c r="G32" t="s">
         <v>111</v>
       </c>
-      <c r="B32" t="s">
-        <v>237</v>
-      </c>
-      <c r="C32" t="s">
-        <v>274</v>
-      </c>
-      <c r="D32" t="s">
-        <v>111</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>112</v>
       </c>
-      <c r="G32"/>
-      <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
         <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
         <v>113</v>
@@ -1869,10 +1905,10 @@
         <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>285</v>
       </c>
       <c r="D34" t="s">
         <v>115</v>
@@ -1888,10 +1924,10 @@
         <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>286</v>
       </c>
       <c r="D35" t="s">
         <v>117</v>
@@ -1907,941 +1943,941 @@
         <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C36" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D36" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B38" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" t="s">
         <v>124</v>
       </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
       <c r="E38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B39" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C39" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C40" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>280</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C42" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C43" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E43" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C44" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E44" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B45" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B46" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C46" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D46" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C47" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
+        <v>296</v>
+      </c>
+      <c r="D48" t="s">
         <v>144</v>
       </c>
-      <c r="D48" t="s">
-        <v>143</v>
-      </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C49" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C50" t="s">
+        <v>298</v>
+      </c>
+      <c r="D50" t="s">
         <v>148</v>
       </c>
-      <c r="D50" t="s">
-        <v>147</v>
-      </c>
       <c r="E50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C51" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" t="s">
         <v>150</v>
       </c>
-      <c r="D51" t="s">
-        <v>149</v>
-      </c>
       <c r="E51" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="D52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B53" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" t="s">
         <v>154</v>
       </c>
-      <c r="D53" t="s">
-        <v>153</v>
-      </c>
       <c r="E53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>289</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E54" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B55" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C56" t="s">
-        <v>291</v>
+        <v>161</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="D57" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B58" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B59" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B60" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C60" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B61" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C62" t="s">
+        <v>306</v>
+      </c>
+      <c r="D62" t="s">
         <v>172</v>
       </c>
-      <c r="D62" t="s">
-        <v>171</v>
-      </c>
       <c r="E62" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C63" t="s">
+        <v>307</v>
+      </c>
+      <c r="D63" t="s">
         <v>174</v>
       </c>
-      <c r="D63" t="s">
-        <v>173</v>
-      </c>
       <c r="E63" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B64" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" t="s">
         <v>176</v>
       </c>
-      <c r="D64" t="s">
-        <v>175</v>
-      </c>
       <c r="E64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C65" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" t="s">
         <v>178</v>
       </c>
-      <c r="D65" t="s">
-        <v>177</v>
-      </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B66" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>297</v>
+        <v>181</v>
       </c>
       <c r="D66" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
+        <v>183</v>
+      </c>
+      <c r="D67" t="s">
         <v>182</v>
       </c>
-      <c r="D67" t="s">
-        <v>181</v>
-      </c>
       <c r="E67" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>298</v>
+        <v>185</v>
       </c>
       <c r="D68" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E68" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C69" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D69" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B70" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C70" t="s">
-        <v>300</v>
+        <v>189</v>
       </c>
       <c r="D70" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E70" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D71" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E71" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="D72" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E72" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C73" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D73" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B74" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C74" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D74" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E74" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C75" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="D75" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C76" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E76" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C77" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="D77" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B78" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C78" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D78" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C79" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D79" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E79" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B80" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C80" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="D80" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E80" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C81" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D81" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C82" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="D82" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E82" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C83" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D83" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E83" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C84" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D84" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E84" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B85" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C85" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D85" t="s">
         <v>218</v>
@@ -2857,10 +2893,10 @@
         <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C86" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
@@ -2876,10 +2912,10 @@
         <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D87" t="s">
         <v>222</v>
@@ -2895,67 +2931,67 @@
         <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="C88" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D88" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s">
+        <v>328</v>
+      </c>
+      <c r="D89" t="s">
         <v>227</v>
       </c>
-      <c r="D89" t="s">
-        <v>226</v>
-      </c>
       <c r="E89" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C90" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E90" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C91" t="s">
-        <v>232</v>
+        <v>330</v>
       </c>
       <c r="D91" t="s">
         <v>231</v>
@@ -2971,7 +3007,7 @@
         <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C92" t="s">
         <v>234</v>
@@ -2984,6 +3020,63 @@
       </c>
       <c r="G92"/>
       <c r="H92"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>235</v>
+      </c>
+      <c r="B93" t="s">
+        <v>257</v>
+      </c>
+      <c r="C93" t="s">
+        <v>331</v>
+      </c>
+      <c r="D93" t="s">
+        <v>235</v>
+      </c>
+      <c r="E93" t="s">
+        <v>236</v>
+      </c>
+      <c r="G93"/>
+      <c r="H93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>237</v>
+      </c>
+      <c r="B94" t="s">
+        <v>248</v>
+      </c>
+      <c r="C94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" t="s">
+        <v>238</v>
+      </c>
+      <c r="E94" t="s">
+        <v>239</v>
+      </c>
+      <c r="G94"/>
+      <c r="H94"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>240</v>
+      </c>
+      <c r="B95" t="s">
+        <v>258</v>
+      </c>
+      <c r="C95" t="s">
+        <v>241</v>
+      </c>
+      <c r="D95" t="s">
+        <v>240</v>
+      </c>
+      <c r="E95" t="s">
+        <v>241</v>
+      </c>
+      <c r="G95"/>
+      <c r="H95"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Game/Race.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="340">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">yerles</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">イエルス</t>
@@ -281,18 +281,6 @@
     <t xml:space="preserve">古代蟹は最も古い蟹の種族で、水辺を好み、生息する地域に適応し様々な属性へと進化しています。基本的には美味しいものの、属性によって風味も変化します。筋力と耐久に秀で、その巨大なハサミで敵を拘束し、また泡のブレスを吐くことができます。</t>
   </si>
   <si>
-    <t xml:space="preserve">ratkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラトキン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">werewolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">人狼</t>
-  </si>
-  <si>
     <t xml:space="preserve">goblin</t>
   </si>
   <si>
@@ -374,15 +362,6 @@
     <t xml:space="preserve">ウサギ</t>
   </si>
   <si>
-    <t xml:space="preserve">rabbitkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ravian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラビアン</t>
-  </si>
-  <si>
     <t xml:space="preserve">sheep</t>
   </si>
   <si>
@@ -770,12 +749,6 @@
     <t xml:space="preserve">Alpha 17.1</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.293</t>
-  </si>
-  <si>
     <t xml:space="preserve">EA 23.278</t>
   </si>
   <si>
@@ -839,12 +812,6 @@
     <t xml:space="preserve">古代螃蟹</t>
   </si>
   <si>
-    <t xml:space="preserve">鼠人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狼人</t>
-  </si>
-  <si>
     <t xml:space="preserve">哥布林</t>
   </si>
   <si>
@@ -876,9 +843,6 @@
   </si>
   <si>
     <t xml:space="preserve">兔子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">兔人</t>
   </si>
   <si>
     <t xml:space="preserve">蜈蚣</t>
@@ -1176,10 +1140,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1188,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1202,10 +1166,10 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -1214,7 +1178,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -1228,7 +1192,7 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -1240,7 +1204,7 @@
         <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="G5" t="s">
         <v>19</v>
@@ -1254,10 +1218,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C6" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -1266,7 +1230,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="G6" t="s">
         <v>24</v>
@@ -1280,10 +1244,10 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
@@ -1292,7 +1256,7 @@
         <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -1306,10 +1270,10 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
         <v>30</v>
@@ -1318,7 +1282,7 @@
         <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="G8" t="s">
         <v>32</v>
@@ -1332,10 +1296,10 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -1344,7 +1308,7 @@
         <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="G9" t="s">
         <v>37</v>
@@ -1358,10 +1322,10 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
@@ -1370,7 +1334,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1384,10 +1348,10 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1396,7 +1360,7 @@
         <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="G11" t="s">
         <v>45</v>
@@ -1410,7 +1374,7 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
         <v>48</v>
@@ -1422,7 +1386,7 @@
         <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="G12" t="s">
         <v>49</v>
@@ -1436,10 +1400,10 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1448,7 +1412,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1462,10 +1426,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
         <v>55</v>
@@ -1474,7 +1438,7 @@
         <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="G14" t="s">
         <v>57</v>
@@ -1488,10 +1452,10 @@
         <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="D15" t="s">
         <v>59</v>
@@ -1500,7 +1464,7 @@
         <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="G15" t="s">
         <v>61</v>
@@ -1514,10 +1478,10 @@
         <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C16" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -1526,7 +1490,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="G16" t="s">
         <v>65</v>
@@ -1540,7 +1504,7 @@
         <v>67</v>
       </c>
       <c r="B17" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
         <v>68</v>
@@ -1552,7 +1516,7 @@
         <v>68</v>
       </c>
       <c r="F17" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="G17" t="s">
         <v>69</v>
@@ -1566,7 +1530,7 @@
         <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C18" t="s">
         <v>72</v>
@@ -1578,7 +1542,7 @@
         <v>72</v>
       </c>
       <c r="F18" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="G18" t="s">
         <v>73</v>
@@ -1592,10 +1556,10 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C19" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>75</v>
@@ -1604,7 +1568,7 @@
         <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="G19" t="s">
         <v>77</v>
@@ -1618,10 +1582,10 @@
         <v>79</v>
       </c>
       <c r="B20" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D20" t="s">
         <v>79</v>
@@ -1630,7 +1594,7 @@
         <v>80</v>
       </c>
       <c r="F20" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="G20" t="s">
         <v>81</v>
@@ -1644,10 +1608,10 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C21" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
         <v>84</v>
@@ -1656,7 +1620,7 @@
         <v>85</v>
       </c>
       <c r="F21" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="G21" t="s">
         <v>86</v>
@@ -1670,10 +1634,10 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C22" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
         <v>88</v>
@@ -1689,48 +1653,48 @@
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G24"/>
       <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D25" t="s">
         <v>95</v>
@@ -1746,10 +1710,10 @@
         <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -1765,10 +1729,10 @@
         <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C27" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s">
         <v>99</v>
@@ -1784,10 +1748,10 @@
         <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D28" t="s">
         <v>101</v>
@@ -1803,10 +1767,10 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D29" t="s">
         <v>103</v>
@@ -1825,7 +1789,7 @@
         <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="D30" t="s">
         <v>105</v>
@@ -1833,63 +1797,63 @@
       <c r="E30" t="s">
         <v>106</v>
       </c>
-      <c r="G30"/>
-      <c r="H30"/>
+      <c r="F30" t="s">
+        <v>339</v>
+      </c>
+      <c r="G30" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C31" t="s">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G31"/>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B32" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
-      </c>
-      <c r="F32" t="s">
-        <v>351</v>
-      </c>
-      <c r="G32" t="s">
-        <v>111</v>
-      </c>
-      <c r="H32" t="s">
         <v>112</v>
       </c>
+      <c r="G32"/>
+      <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
         <v>113</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="D33" t="s">
         <v>113</v>
@@ -1905,10 +1869,10 @@
         <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>285</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>115</v>
@@ -1924,10 +1888,10 @@
         <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C35" t="s">
-        <v>286</v>
+        <v>118</v>
       </c>
       <c r="D35" t="s">
         <v>117</v>
@@ -1943,941 +1907,941 @@
         <v>119</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="D36" t="s">
+        <v>119</v>
+      </c>
+      <c r="E36" t="s">
         <v>120</v>
-      </c>
-      <c r="E36" t="s">
-        <v>121</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>121</v>
+      </c>
+      <c r="B37" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D37" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" t="s">
         <v>122</v>
-      </c>
-      <c r="B37" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" t="s">
-        <v>122</v>
-      </c>
-      <c r="E37" t="s">
-        <v>123</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>123</v>
+      </c>
+      <c r="B38" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" t="s">
         <v>124</v>
       </c>
-      <c r="B38" t="s">
-        <v>244</v>
-      </c>
-      <c r="C38" t="s">
-        <v>125</v>
-      </c>
       <c r="D38" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" t="s">
         <v>124</v>
-      </c>
-      <c r="E38" t="s">
-        <v>125</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>125</v>
+      </c>
+      <c r="B39" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" t="s">
+        <v>278</v>
+      </c>
+      <c r="D39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" t="s">
         <v>126</v>
-      </c>
-      <c r="B39" t="s">
-        <v>244</v>
-      </c>
-      <c r="C39" t="s">
-        <v>288</v>
-      </c>
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-      <c r="E39" t="s">
-        <v>127</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B40" t="s">
+        <v>237</v>
+      </c>
+      <c r="C40" t="s">
+        <v>279</v>
+      </c>
+      <c r="D40" t="s">
+        <v>127</v>
+      </c>
+      <c r="E40" t="s">
         <v>128</v>
-      </c>
-      <c r="B40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C40" t="s">
-        <v>289</v>
-      </c>
-      <c r="D40" t="s">
-        <v>128</v>
-      </c>
-      <c r="E40" t="s">
-        <v>129</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" t="s">
+        <v>237</v>
+      </c>
+      <c r="C41" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" t="s">
         <v>130</v>
-      </c>
-      <c r="B41" t="s">
-        <v>254</v>
-      </c>
-      <c r="C41" t="s">
-        <v>131</v>
-      </c>
-      <c r="D41" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" t="s">
-        <v>131</v>
       </c>
       <c r="G41"/>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" t="s">
+        <v>131</v>
+      </c>
+      <c r="E42" t="s">
         <v>132</v>
-      </c>
-      <c r="B42" t="s">
-        <v>244</v>
-      </c>
-      <c r="C42" t="s">
-        <v>290</v>
-      </c>
-      <c r="D42" t="s">
-        <v>132</v>
-      </c>
-      <c r="E42" t="s">
-        <v>133</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>133</v>
+      </c>
+      <c r="B43" t="s">
+        <v>237</v>
+      </c>
+      <c r="C43" t="s">
+        <v>282</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" t="s">
         <v>134</v>
-      </c>
-      <c r="B43" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" t="s">
-        <v>291</v>
-      </c>
-      <c r="D43" t="s">
-        <v>134</v>
-      </c>
-      <c r="E43" t="s">
-        <v>135</v>
       </c>
       <c r="G43"/>
       <c r="H43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" t="s">
+        <v>237</v>
+      </c>
+      <c r="C44" t="s">
+        <v>283</v>
+      </c>
+      <c r="D44" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" t="s">
         <v>136</v>
-      </c>
-      <c r="B44" t="s">
-        <v>244</v>
-      </c>
-      <c r="C44" t="s">
-        <v>292</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" t="s">
-        <v>137</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" t="s">
+        <v>284</v>
+      </c>
+      <c r="D45" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" t="s">
         <v>138</v>
-      </c>
-      <c r="B45" t="s">
-        <v>244</v>
-      </c>
-      <c r="C45" t="s">
-        <v>293</v>
-      </c>
-      <c r="D45" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" t="s">
-        <v>139</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" t="s">
+        <v>285</v>
+      </c>
+      <c r="D46" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" t="s">
         <v>140</v>
-      </c>
-      <c r="B46" t="s">
-        <v>244</v>
-      </c>
-      <c r="C46" t="s">
-        <v>294</v>
-      </c>
-      <c r="D46" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" t="s">
-        <v>141</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" t="s">
         <v>142</v>
-      </c>
-      <c r="B47" t="s">
-        <v>244</v>
-      </c>
-      <c r="C47" t="s">
-        <v>295</v>
-      </c>
-      <c r="D47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E47" t="s">
-        <v>143</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B48" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" t="s">
         <v>144</v>
       </c>
-      <c r="B48" t="s">
-        <v>244</v>
-      </c>
-      <c r="C48" t="s">
-        <v>296</v>
-      </c>
       <c r="D48" t="s">
+        <v>143</v>
+      </c>
+      <c r="E48" t="s">
         <v>144</v>
-      </c>
-      <c r="E48" t="s">
-        <v>145</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>145</v>
+      </c>
+      <c r="B49" t="s">
+        <v>237</v>
+      </c>
+      <c r="C49" t="s">
+        <v>287</v>
+      </c>
+      <c r="D49" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" t="s">
         <v>146</v>
-      </c>
-      <c r="B49" t="s">
-        <v>244</v>
-      </c>
-      <c r="C49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D49" t="s">
-        <v>146</v>
-      </c>
-      <c r="E49" t="s">
-        <v>147</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" t="s">
         <v>148</v>
       </c>
-      <c r="B50" t="s">
-        <v>244</v>
-      </c>
-      <c r="C50" t="s">
-        <v>298</v>
-      </c>
       <c r="D50" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50" t="s">
         <v>148</v>
-      </c>
-      <c r="E50" t="s">
-        <v>149</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" t="s">
+        <v>237</v>
+      </c>
+      <c r="C51" t="s">
         <v>150</v>
       </c>
-      <c r="B51" t="s">
-        <v>244</v>
-      </c>
-      <c r="C51" t="s">
-        <v>151</v>
-      </c>
       <c r="D51" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51" t="s">
         <v>150</v>
-      </c>
-      <c r="E51" t="s">
-        <v>151</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>151</v>
+      </c>
+      <c r="B52" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52" t="s">
+        <v>151</v>
+      </c>
+      <c r="E52" t="s">
         <v>152</v>
-      </c>
-      <c r="B52" t="s">
-        <v>244</v>
-      </c>
-      <c r="C52" t="s">
-        <v>299</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
-        <v>153</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" t="s">
         <v>154</v>
       </c>
-      <c r="B53" t="s">
-        <v>244</v>
-      </c>
-      <c r="C53" t="s">
-        <v>155</v>
-      </c>
       <c r="D53" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" t="s">
         <v>154</v>
-      </c>
-      <c r="E53" t="s">
-        <v>155</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>155</v>
+      </c>
+      <c r="B54" t="s">
+        <v>237</v>
+      </c>
+      <c r="C54" t="s">
+        <v>289</v>
+      </c>
+      <c r="D54" t="s">
+        <v>155</v>
+      </c>
+      <c r="E54" t="s">
         <v>156</v>
-      </c>
-      <c r="B54" t="s">
-        <v>244</v>
-      </c>
-      <c r="C54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D54" t="s">
-        <v>156</v>
-      </c>
-      <c r="E54" t="s">
-        <v>157</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" t="s">
+        <v>237</v>
+      </c>
+      <c r="C55" t="s">
+        <v>290</v>
+      </c>
+      <c r="D55" t="s">
+        <v>157</v>
+      </c>
+      <c r="E55" t="s">
         <v>158</v>
-      </c>
-      <c r="B55" t="s">
-        <v>244</v>
-      </c>
-      <c r="C55" t="s">
-        <v>300</v>
-      </c>
-      <c r="D55" t="s">
-        <v>158</v>
-      </c>
-      <c r="E55" t="s">
-        <v>159</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>159</v>
+      </c>
+      <c r="B56" t="s">
+        <v>237</v>
+      </c>
+      <c r="C56" t="s">
+        <v>291</v>
+      </c>
+      <c r="D56" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" t="s">
         <v>160</v>
-      </c>
-      <c r="B56" t="s">
-        <v>244</v>
-      </c>
-      <c r="C56" t="s">
-        <v>161</v>
-      </c>
-      <c r="D56" t="s">
-        <v>160</v>
-      </c>
-      <c r="E56" t="s">
-        <v>161</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>161</v>
+      </c>
+      <c r="B57" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" t="s">
+        <v>292</v>
+      </c>
+      <c r="D57" t="s">
+        <v>161</v>
+      </c>
+      <c r="E57" t="s">
         <v>162</v>
-      </c>
-      <c r="B57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C57" t="s">
-        <v>301</v>
-      </c>
-      <c r="D57" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" t="s">
-        <v>163</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>163</v>
+      </c>
+      <c r="B58" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" t="s">
+        <v>293</v>
+      </c>
+      <c r="D58" t="s">
+        <v>163</v>
+      </c>
+      <c r="E58" t="s">
         <v>164</v>
-      </c>
-      <c r="B58" t="s">
-        <v>244</v>
-      </c>
-      <c r="C58" t="s">
-        <v>302</v>
-      </c>
-      <c r="D58" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" t="s">
-        <v>165</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>165</v>
+      </c>
+      <c r="B59" t="s">
+        <v>237</v>
+      </c>
+      <c r="C59" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" t="s">
         <v>166</v>
-      </c>
-      <c r="B59" t="s">
-        <v>244</v>
-      </c>
-      <c r="C59" t="s">
-        <v>303</v>
-      </c>
-      <c r="D59" t="s">
-        <v>166</v>
-      </c>
-      <c r="E59" t="s">
-        <v>167</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>167</v>
+      </c>
+      <c r="B60" t="s">
+        <v>237</v>
+      </c>
+      <c r="C60" t="s">
+        <v>295</v>
+      </c>
+      <c r="D60" t="s">
+        <v>167</v>
+      </c>
+      <c r="E60" t="s">
         <v>168</v>
-      </c>
-      <c r="B60" t="s">
-        <v>244</v>
-      </c>
-      <c r="C60" t="s">
-        <v>304</v>
-      </c>
-      <c r="D60" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" t="s">
-        <v>169</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>169</v>
+      </c>
+      <c r="B61" t="s">
+        <v>237</v>
+      </c>
+      <c r="C61" t="s">
+        <v>296</v>
+      </c>
+      <c r="D61" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61" t="s">
         <v>170</v>
-      </c>
-      <c r="B61" t="s">
-        <v>244</v>
-      </c>
-      <c r="C61" t="s">
-        <v>305</v>
-      </c>
-      <c r="D61" t="s">
-        <v>170</v>
-      </c>
-      <c r="E61" t="s">
-        <v>171</v>
       </c>
       <c r="G61"/>
       <c r="H61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>171</v>
+      </c>
+      <c r="B62" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" t="s">
         <v>172</v>
       </c>
-      <c r="B62" t="s">
-        <v>244</v>
-      </c>
-      <c r="C62" t="s">
-        <v>306</v>
-      </c>
       <c r="D62" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" t="s">
         <v>172</v>
-      </c>
-      <c r="E62" t="s">
-        <v>173</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>173</v>
+      </c>
+      <c r="B63" t="s">
+        <v>237</v>
+      </c>
+      <c r="C63" t="s">
         <v>174</v>
       </c>
-      <c r="B63" t="s">
-        <v>244</v>
-      </c>
-      <c r="C63" t="s">
-        <v>307</v>
-      </c>
       <c r="D63" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" t="s">
         <v>174</v>
-      </c>
-      <c r="E63" t="s">
-        <v>175</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" t="s">
+        <v>237</v>
+      </c>
+      <c r="C64" t="s">
         <v>176</v>
       </c>
-      <c r="B64" t="s">
-        <v>244</v>
-      </c>
-      <c r="C64" t="s">
-        <v>308</v>
-      </c>
       <c r="D64" t="s">
+        <v>175</v>
+      </c>
+      <c r="E64" t="s">
         <v>176</v>
-      </c>
-      <c r="E64" t="s">
-        <v>177</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>177</v>
+      </c>
+      <c r="B65" t="s">
+        <v>237</v>
+      </c>
+      <c r="C65" t="s">
         <v>178</v>
       </c>
-      <c r="B65" t="s">
-        <v>244</v>
-      </c>
-      <c r="C65" t="s">
-        <v>179</v>
-      </c>
       <c r="D65" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" t="s">
         <v>178</v>
-      </c>
-      <c r="E65" t="s">
-        <v>179</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>179</v>
+      </c>
+      <c r="B66" t="s">
+        <v>237</v>
+      </c>
+      <c r="C66" t="s">
+        <v>297</v>
+      </c>
+      <c r="D66" t="s">
+        <v>179</v>
+      </c>
+      <c r="E66" t="s">
         <v>180</v>
-      </c>
-      <c r="B66" t="s">
-        <v>244</v>
-      </c>
-      <c r="C66" t="s">
-        <v>181</v>
-      </c>
-      <c r="D66" t="s">
-        <v>180</v>
-      </c>
-      <c r="E66" t="s">
-        <v>181</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" t="s">
+        <v>237</v>
+      </c>
+      <c r="C67" t="s">
         <v>182</v>
       </c>
-      <c r="B67" t="s">
-        <v>244</v>
-      </c>
-      <c r="C67" t="s">
-        <v>183</v>
-      </c>
       <c r="D67" t="s">
+        <v>181</v>
+      </c>
+      <c r="E67" t="s">
         <v>182</v>
-      </c>
-      <c r="E67" t="s">
-        <v>183</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>183</v>
+      </c>
+      <c r="B68" t="s">
+        <v>237</v>
+      </c>
+      <c r="C68" t="s">
+        <v>298</v>
+      </c>
+      <c r="D68" t="s">
+        <v>183</v>
+      </c>
+      <c r="E68" t="s">
         <v>184</v>
-      </c>
-      <c r="B68" t="s">
-        <v>244</v>
-      </c>
-      <c r="C68" t="s">
-        <v>185</v>
-      </c>
-      <c r="D68" t="s">
-        <v>184</v>
-      </c>
-      <c r="E68" t="s">
-        <v>185</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" t="s">
+        <v>237</v>
+      </c>
+      <c r="C69" t="s">
+        <v>299</v>
+      </c>
+      <c r="D69" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" t="s">
         <v>186</v>
-      </c>
-      <c r="B69" t="s">
-        <v>244</v>
-      </c>
-      <c r="C69" t="s">
-        <v>309</v>
-      </c>
-      <c r="D69" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" t="s">
-        <v>187</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" t="s">
+        <v>241</v>
+      </c>
+      <c r="C70" t="s">
+        <v>300</v>
+      </c>
+      <c r="D70" t="s">
+        <v>187</v>
+      </c>
+      <c r="E70" t="s">
         <v>188</v>
-      </c>
-      <c r="B70" t="s">
-        <v>244</v>
-      </c>
-      <c r="C70" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" t="s">
-        <v>189</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" t="s">
+        <v>301</v>
+      </c>
+      <c r="D71" t="s">
+        <v>189</v>
+      </c>
+      <c r="E71" t="s">
         <v>190</v>
-      </c>
-      <c r="B71" t="s">
-        <v>244</v>
-      </c>
-      <c r="C71" t="s">
-        <v>310</v>
-      </c>
-      <c r="D71" t="s">
-        <v>190</v>
-      </c>
-      <c r="E71" t="s">
-        <v>191</v>
       </c>
       <c r="G71"/>
       <c r="H71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" t="s">
+        <v>237</v>
+      </c>
+      <c r="C72" t="s">
+        <v>302</v>
+      </c>
+      <c r="D72" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" t="s">
         <v>192</v>
-      </c>
-      <c r="B72" t="s">
-        <v>244</v>
-      </c>
-      <c r="C72" t="s">
-        <v>311</v>
-      </c>
-      <c r="D72" t="s">
-        <v>192</v>
-      </c>
-      <c r="E72" t="s">
-        <v>193</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" t="s">
+        <v>237</v>
+      </c>
+      <c r="C73" t="s">
+        <v>303</v>
+      </c>
+      <c r="D73" t="s">
+        <v>193</v>
+      </c>
+      <c r="E73" t="s">
         <v>194</v>
-      </c>
-      <c r="B73" t="s">
-        <v>248</v>
-      </c>
-      <c r="C73" t="s">
-        <v>312</v>
-      </c>
-      <c r="D73" t="s">
-        <v>194</v>
-      </c>
-      <c r="E73" t="s">
-        <v>195</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" t="s">
+        <v>237</v>
+      </c>
+      <c r="C74" t="s">
+        <v>304</v>
+      </c>
+      <c r="D74" t="s">
+        <v>195</v>
+      </c>
+      <c r="E74" t="s">
         <v>196</v>
-      </c>
-      <c r="B74" t="s">
-        <v>244</v>
-      </c>
-      <c r="C74" t="s">
-        <v>313</v>
-      </c>
-      <c r="D74" t="s">
-        <v>196</v>
-      </c>
-      <c r="E74" t="s">
-        <v>197</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75" t="s">
+        <v>237</v>
+      </c>
+      <c r="C75" t="s">
+        <v>305</v>
+      </c>
+      <c r="D75" t="s">
+        <v>197</v>
+      </c>
+      <c r="E75" t="s">
         <v>198</v>
-      </c>
-      <c r="B75" t="s">
-        <v>244</v>
-      </c>
-      <c r="C75" t="s">
-        <v>314</v>
-      </c>
-      <c r="D75" t="s">
-        <v>198</v>
-      </c>
-      <c r="E75" t="s">
-        <v>199</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>199</v>
+      </c>
+      <c r="B76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C76" t="s">
+        <v>306</v>
+      </c>
+      <c r="D76" t="s">
+        <v>199</v>
+      </c>
+      <c r="E76" t="s">
         <v>200</v>
-      </c>
-      <c r="B76" t="s">
-        <v>244</v>
-      </c>
-      <c r="C76" t="s">
-        <v>315</v>
-      </c>
-      <c r="D76" t="s">
-        <v>200</v>
-      </c>
-      <c r="E76" t="s">
-        <v>201</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>201</v>
+      </c>
+      <c r="B77" t="s">
+        <v>237</v>
+      </c>
+      <c r="C77" t="s">
+        <v>307</v>
+      </c>
+      <c r="D77" t="s">
+        <v>201</v>
+      </c>
+      <c r="E77" t="s">
         <v>202</v>
-      </c>
-      <c r="B77" t="s">
-        <v>244</v>
-      </c>
-      <c r="C77" t="s">
-        <v>316</v>
-      </c>
-      <c r="D77" t="s">
-        <v>202</v>
-      </c>
-      <c r="E77" t="s">
-        <v>203</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s">
+        <v>308</v>
+      </c>
+      <c r="D78" t="s">
+        <v>203</v>
+      </c>
+      <c r="E78" t="s">
         <v>204</v>
-      </c>
-      <c r="B78" t="s">
-        <v>244</v>
-      </c>
-      <c r="C78" t="s">
-        <v>317</v>
-      </c>
-      <c r="D78" t="s">
-        <v>204</v>
-      </c>
-      <c r="E78" t="s">
-        <v>205</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>205</v>
+      </c>
+      <c r="B79" t="s">
+        <v>246</v>
+      </c>
+      <c r="C79" t="s">
+        <v>309</v>
+      </c>
+      <c r="D79" t="s">
+        <v>205</v>
+      </c>
+      <c r="E79" t="s">
         <v>206</v>
-      </c>
-      <c r="B79" t="s">
-        <v>244</v>
-      </c>
-      <c r="C79" t="s">
-        <v>318</v>
-      </c>
-      <c r="D79" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" t="s">
-        <v>207</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>207</v>
+      </c>
+      <c r="B80" t="s">
+        <v>237</v>
+      </c>
+      <c r="C80" t="s">
+        <v>310</v>
+      </c>
+      <c r="D80" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" t="s">
         <v>208</v>
-      </c>
-      <c r="B80" t="s">
-        <v>244</v>
-      </c>
-      <c r="C80" t="s">
-        <v>319</v>
-      </c>
-      <c r="D80" t="s">
-        <v>208</v>
-      </c>
-      <c r="E80" t="s">
-        <v>209</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>209</v>
+      </c>
+      <c r="B81" t="s">
+        <v>237</v>
+      </c>
+      <c r="C81" t="s">
+        <v>311</v>
+      </c>
+      <c r="D81" t="s">
+        <v>209</v>
+      </c>
+      <c r="E81" t="s">
         <v>210</v>
-      </c>
-      <c r="B81" t="s">
-        <v>244</v>
-      </c>
-      <c r="C81" t="s">
-        <v>320</v>
-      </c>
-      <c r="D81" t="s">
-        <v>210</v>
-      </c>
-      <c r="E81" t="s">
-        <v>211</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>211</v>
+      </c>
+      <c r="B82" t="s">
+        <v>237</v>
+      </c>
+      <c r="C82" t="s">
+        <v>312</v>
+      </c>
+      <c r="D82" t="s">
+        <v>211</v>
+      </c>
+      <c r="E82" t="s">
         <v>212</v>
-      </c>
-      <c r="B82" t="s">
-        <v>255</v>
-      </c>
-      <c r="C82" t="s">
-        <v>321</v>
-      </c>
-      <c r="D82" t="s">
-        <v>212</v>
-      </c>
-      <c r="E82" t="s">
-        <v>213</v>
       </c>
       <c r="G82"/>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>213</v>
+      </c>
+      <c r="B83" t="s">
+        <v>237</v>
+      </c>
+      <c r="C83" t="s">
+        <v>313</v>
+      </c>
+      <c r="D83" t="s">
+        <v>213</v>
+      </c>
+      <c r="E83" t="s">
         <v>214</v>
-      </c>
-      <c r="B83" t="s">
-        <v>244</v>
-      </c>
-      <c r="C83" t="s">
-        <v>322</v>
-      </c>
-      <c r="D83" t="s">
-        <v>214</v>
-      </c>
-      <c r="E83" t="s">
-        <v>215</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>215</v>
+      </c>
+      <c r="B84" t="s">
+        <v>237</v>
+      </c>
+      <c r="C84" t="s">
+        <v>314</v>
+      </c>
+      <c r="D84" t="s">
+        <v>215</v>
+      </c>
+      <c r="E84" t="s">
         <v>216</v>
-      </c>
-      <c r="B84" t="s">
-        <v>244</v>
-      </c>
-      <c r="C84" t="s">
-        <v>323</v>
-      </c>
-      <c r="D84" t="s">
-        <v>216</v>
-      </c>
-      <c r="E84" t="s">
-        <v>217</v>
       </c>
       <c r="G84"/>
       <c r="H84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="D85" t="s">
         <v>218</v>
@@ -2893,10 +2857,10 @@
         <v>220</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="D86" t="s">
         <v>220</v>
@@ -2912,10 +2876,10 @@
         <v>222</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="C87" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D87" t="s">
         <v>222</v>
@@ -2931,67 +2895,67 @@
         <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D88" t="s">
+        <v>224</v>
+      </c>
+      <c r="E88" t="s">
         <v>225</v>
-      </c>
-      <c r="E88" t="s">
-        <v>226</v>
       </c>
       <c r="G88"/>
       <c r="H88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
+        <v>226</v>
+      </c>
+      <c r="B89" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" t="s">
         <v>227</v>
       </c>
-      <c r="B89" t="s">
-        <v>244</v>
-      </c>
-      <c r="C89" t="s">
-        <v>328</v>
-      </c>
       <c r="D89" t="s">
+        <v>226</v>
+      </c>
+      <c r="E89" t="s">
         <v>227</v>
-      </c>
-      <c r="E89" t="s">
-        <v>228</v>
       </c>
       <c r="G89"/>
       <c r="H89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>228</v>
+      </c>
+      <c r="B90" t="s">
+        <v>248</v>
+      </c>
+      <c r="C90" t="s">
+        <v>319</v>
+      </c>
+      <c r="D90" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" t="s">
         <v>229</v>
-      </c>
-      <c r="B90" t="s">
-        <v>244</v>
-      </c>
-      <c r="C90" t="s">
-        <v>329</v>
-      </c>
-      <c r="D90" t="s">
-        <v>229</v>
-      </c>
-      <c r="E90" t="s">
-        <v>230</v>
       </c>
       <c r="G90"/>
       <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C91" t="s">
-        <v>330</v>
+        <v>232</v>
       </c>
       <c r="D91" t="s">
         <v>231</v>
@@ -3007,7 +2971,7 @@
         <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C92" t="s">
         <v>234</v>
@@ -3020,63 +2984,6 @@
       </c>
       <c r="G92"/>
       <c r="H92"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>235</v>
-      </c>
-      <c r="B93" t="s">
-        <v>257</v>
-      </c>
-      <c r="C93" t="s">
-        <v>331</v>
-      </c>
-      <c r="D93" t="s">
-        <v>235</v>
-      </c>
-      <c r="E93" t="s">
-        <v>236</v>
-      </c>
-      <c r="G93"/>
-      <c r="H93"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>237</v>
-      </c>
-      <c r="B94" t="s">
-        <v>248</v>
-      </c>
-      <c r="C94" t="s">
-        <v>239</v>
-      </c>
-      <c r="D94" t="s">
-        <v>238</v>
-      </c>
-      <c r="E94" t="s">
-        <v>239</v>
-      </c>
-      <c r="G94"/>
-      <c r="H94"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>240</v>
-      </c>
-      <c r="B95" t="s">
-        <v>258</v>
-      </c>
-      <c r="C95" t="s">
-        <v>241</v>
-      </c>
-      <c r="D95" t="s">
-        <v>240</v>
-      </c>
-      <c r="E95" t="s">
-        <v>241</v>
-      </c>
-      <c r="G95"/>
-      <c r="H95"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
